--- a/writing-b52-a9-manuscript-page-ledger-recompute/environment/input/edit_register.xlsx
+++ b/writing-b52-a9-manuscript-page-ledger-recompute/environment/input/edit_register.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="About" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tally" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Not in" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,10 +53,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,16 +428,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,12 +458,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>line_change</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>edit_state</t>
+          <t>proposed_change</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -467,7 +473,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>decision</t>
         </is>
       </c>
     </row>
@@ -485,14 +491,14 @@
           <t>PS-01</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Restore the epigraph dropped from the draft</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -500,7 +506,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Restore the epigraph dropped from the draft</t>
+          <t>Yes, take it.</t>
         </is>
       </c>
     </row>
@@ -518,14 +524,14 @@
           <t>PS-03</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tighten the exchange on the station platform</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>-3</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -533,7 +539,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tighten the exchange on the station platform</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
@@ -551,14 +557,14 @@
           <t>PS-04</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Cut the dream sequence</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>-22</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -566,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cut the dream sequence</t>
+          <t>Yes, cut the whole sequence.</t>
         </is>
       </c>
     </row>
@@ -584,14 +590,14 @@
           <t>PS-06</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Expand Wren's letter</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -599,7 +605,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Expand Wren's letter</t>
+          <t>Park until the author has read it.</t>
         </is>
       </c>
     </row>
@@ -617,14 +623,14 @@
           <t>PS-07</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cut the harbour flashback</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>-21</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -632,7 +638,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cut the harbour flashback</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
@@ -650,14 +656,14 @@
           <t>PS-08</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Restore the two lines of the ferry song</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -665,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Restore the two lines of the ferry song</t>
+          <t>Fine as proposed.</t>
         </is>
       </c>
     </row>
@@ -683,14 +689,14 @@
           <t>PS-10</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Add a coda to the market scene</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>14</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -698,7 +704,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Add a coda to the market scene</t>
+          <t>Park until the author has read it.</t>
         </is>
       </c>
     </row>
@@ -716,14 +722,14 @@
           <t>PS-11</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Trim the weather paragraph</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>-4</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -731,7 +737,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trim the weather paragraph</t>
+          <t>Yes, take it.</t>
         </is>
       </c>
     </row>
@@ -749,14 +755,14 @@
           <t>PS-13</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Compress the inquest testimony</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>-6</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -764,7 +770,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Compress the inquest testimony</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
@@ -782,14 +788,14 @@
           <t>PS-13</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Add the coroner's closing line</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -797,7 +803,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Add the coroner's closing line</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
@@ -815,14 +821,14 @@
           <t>PS-15</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Restore the list of ship names</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -830,7 +836,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Restore the list of ship names</t>
+          <t>No. The list of ship names stays out.</t>
         </is>
       </c>
     </row>
@@ -848,14 +854,14 @@
           <t>PS-16</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cut the second telling of the wreck</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>-9</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -863,7 +869,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cut the second telling of the wreck</t>
+          <t>Yes, take it.</t>
         </is>
       </c>
     </row>
@@ -881,14 +887,14 @@
           <t>PS-18</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Add the lighthouse keeper's log entry</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -896,7 +902,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Add the lighthouse keeper's log entry</t>
+          <t>Park until the author has read it.</t>
         </is>
       </c>
     </row>
@@ -914,14 +920,14 @@
           <t>PS-20</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Trim the auction catalogue</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>-7</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -929,7 +935,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Trim the auction catalogue</t>
+          <t>Yes, but only five lines out, not seven.</t>
         </is>
       </c>
     </row>
@@ -947,14 +953,14 @@
           <t>PS-22</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Restore Maud's reply</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>2</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -962,7 +968,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Restore Maud's reply</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
@@ -980,14 +986,14 @@
           <t>PS-24</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cut the recipe interlude</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>-11</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -995,7 +1001,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cut the recipe interlude</t>
+          <t>Yes, the whole interlude goes.</t>
         </is>
       </c>
     </row>
@@ -1013,14 +1019,14 @@
           <t>PS-25</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Expand the storm at the quay</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>6</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -1028,7 +1034,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Expand the storm at the quay</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
@@ -1046,14 +1052,14 @@
           <t>PS-28</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Trim the sermon</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>-5</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Ines</t>
@@ -1061,7 +1067,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Trim the sermon</t>
+          <t>Fine as proposed.</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1085,9 @@
           <t>PS-01</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Restore the epigraph dropped from the draft</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1094,7 +1097,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Restore the epigraph dropped from the draft</t>
+          <t>Yes, but six lines, not four.</t>
         </is>
       </c>
     </row>
@@ -1112,14 +1115,14 @@
           <t>PS-02</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Drop the repeated greeting</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>-2</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>Tomas</t>
@@ -1127,7 +1130,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Drop the repeated greeting</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1148,9 @@
           <t>PS-04</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>-22</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Cut the dream sequence</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cut the dream sequence</t>
+          <t>On reflection, leave this for the author.</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,9 @@
           <t>PS-08</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Restore the two lines of the ferry song</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1193,30 +1190,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Restore the two lines of the ferry song</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ED-07</t>
+          <t>ED-15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PS-10</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>14</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
+          <t>PS-20</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Trim the auction catalogue</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1226,7 +1220,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Add a coda to the market scene</t>
+          <t>Park until the author has read it.</t>
         </is>
       </c>
     </row>
@@ -1236,20 +1230,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ED-09</t>
+          <t>ED-07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PS-07</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
+          <t>PS-10</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Add a coda to the market scene</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1259,31 +1250,31 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Drop the second foghorn paragraph</t>
+          <t>Author says go ahead.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ED-21</t>
+          <t>ED-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PS-19</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
+          <t>PS-07</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Drop the second foghorn paragraph</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>-5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1292,7 +1283,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Add the harbourmaster's warning</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
@@ -1302,21 +1293,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ED-13</t>
+          <t>ED-21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PS-16</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>-12</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
+          <t>PS-19</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Add the harbourmaster's warning</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1325,30 +1316,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cut the second telling of the wreck</t>
+          <t>Park until the author has read it.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ED-22</t>
+          <t>ED-13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PS-27</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
+          <t>PS-16</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Cut the second telling of the wreck</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1358,7 +1346,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tighten the reading of the will</t>
+          <t>Yes, and take the next three lines with it: twelve out.</t>
         </is>
       </c>
     </row>
@@ -1368,21 +1356,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ED-17</t>
+          <t>ED-22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PS-24</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>-11</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
+          <t>PS-27</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tighten the reading of the will</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>-4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1391,40 +1379,133 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cut the recipe interlude</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ED-17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PS-24</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cut the recipe interlude</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No. The author wants the interlude kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ED-24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PS-26</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Add a postscript to the letter</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Withdrawn: the letter stays as drafted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
         <v>46277</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>ED-23</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>PS-29</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Restore the last line of the postcard</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
         <v>2</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Tomas</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Restore the last line of the postcard</t>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Agreed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ED-15</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PS-20</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Trim the auction catalogue</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Back to Ines's call.</t>
         </is>
       </c>
     </row>
@@ -1439,43 +1520,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Edit register, Everly manuscript: both reads</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Log: one line per entry, in the order the entries were made. A line is added when an edit is proposed, and a new line is added whenever the call on an edit is revisited; from then on the edit's latest line is its call, with that line's line change and state. Nothing is struck: earlier lines stay as the record of earlier calls.</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Log: one line per decision on an edit, in the order the decisions were made, in the reader's own words. An edit's first line gives its line change as proposed; later lines for the same edit leave proposed_change blank. An edit's latest decision is its call.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>A call is one of three. Accepted: the edit goes in, with the number of lines the decision gives, or, if it gives none, the edit's number as it last stood. Deferred: the edit is parked for the author; it does not go in, and it stays open against its passage. Withdrawn: the edit is turned down; it does not go in, and nothing stays open. A decision that returns an edit to an earlier call makes the edit stand as that call did.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>First read (Ines): 3 to 21 August. Second read (Tomas): 7 to 12 September.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tally: Ines's sum at the end of the first read. For each passage, the total line change of its accepted edits and whether it was left carrying a deferred edit. Not updated since 21 August.</t>
+      <c r="A6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Not in: Tomas's list, at the end of the second read, of the edits that are not going into this pass.</t>
         </is>
       </c>
     </row>
@@ -1490,473 +1578,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>edit_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>passage_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>accepted_line_change</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>deferred_edit</t>
+          <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PS-01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>4</v>
+          <t>ED-03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PS-04</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Cut the dream sequence</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PS-02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
+          <t>ED-04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PS-06</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Expand Wren's letter</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PS-03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>-3</v>
+          <t>ED-12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PS-15</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Restore the list of ship names</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PS-04</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-22</v>
+          <t>ED-14</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PS-18</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Add the lighthouse keeper's log entry</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PS-05</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
+          <t>ED-17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PS-24</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Cut the recipe interlude</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PS-06</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
+          <t>ED-21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PS-19</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Add the harbourmaster's warning</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PS-07</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>-21</v>
+          <t>ED-24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PS-26</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>PS-08</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PS-09</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PS-10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PS-11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-4</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PS-12</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PS-13</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-3</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PS-14</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PS-15</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PS-16</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-9</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PS-17</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PS-18</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PS-19</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PS-20</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>-7</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PS-21</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PS-22</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>PS-23</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PS-24</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-11</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PS-25</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PS-26</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>PS-27</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>PS-28</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>-5</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PS-29</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PS-30</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>Add a postscript to the letter</t>
         </is>
       </c>
     </row>

--- a/writing-b52-a9-manuscript-page-ledger-recompute/environment/input/edit_register.xlsx
+++ b/writing-b52-a9-manuscript-page-ledger-recompute/environment/input/edit_register.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Agreed.</t>
+          <t>Ditto.</t>
         </is>
       </c>
     </row>
@@ -875,21 +875,21 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ED-14</t>
+          <t>ED-39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PS-18</t>
+          <t>PS-09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Add the lighthouse keeper's log entry</t>
+          <t>Restore the dropped stanza</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -902,31 +902,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Park until the author has read it.</t>
+          <t>Hold it.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ED-15</t>
+          <t>ED-14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PS-20</t>
+          <t>PS-18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Trim the auction catalogue</t>
+          <t>Add the lighthouse keeper's log entry</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -935,31 +935,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes, but only five lines out, not seven.</t>
+          <t>Park until the author has read it.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ED-16</t>
+          <t>ED-40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PS-22</t>
+          <t>PS-17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Restore Maud's reply</t>
+          <t>Cut the description of the pier</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -968,31 +968,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Agreed.</t>
+          <t>Go ahead.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ED-17</t>
+          <t>ED-15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PS-24</t>
+          <t>PS-20</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cut the recipe interlude</t>
+          <t>Trim the auction catalogue</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1001,31 +1001,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes, the whole interlude goes.</t>
+          <t>Yes, but only five lines out, not seven.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ED-18</t>
+          <t>ED-41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PS-25</t>
+          <t>PS-14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Expand the storm at the quay</t>
+          <t>Add the ferryman's line</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1034,31 +1034,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Agreed.</t>
+          <t>Drop it.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ED-19</t>
+          <t>ED-16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PS-28</t>
+          <t>PS-22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Trim the sermon</t>
+          <t>Restore Maud's reply</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1067,276 +1067,291 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fine as proposed.</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46272</v>
+        <v>46253</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>ED-17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PS-01</t>
+          <t>PS-24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Restore the epigraph dropped from the draft</t>
-        </is>
+          <t>Cut the recipe interlude</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>-11</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Ines</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes, but six lines, not four.</t>
+          <t>Yes, the whole interlude goes.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46272</v>
+        <v>46253</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ED-20</t>
+          <t>ED-25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PS-02</t>
+          <t>PS-31</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Drop the repeated greeting</t>
+          <t>Cut the second description of the chapel</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Ines</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Agreed.</t>
+          <t>Cut, but six lines only.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46273</v>
+        <v>46254</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ED-03</t>
+          <t>ED-18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PS-04</t>
+          <t>PS-25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cut the dream sequence</t>
-        </is>
+          <t>Expand the storm at the quay</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Ines</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>On reflection, leave this for the author.</t>
+          <t>Agreed.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46273</v>
+        <v>46254</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ED-06</t>
+          <t>ED-26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PS-08</t>
+          <t>PS-32</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Restore the two lines of the ferry song</t>
-        </is>
+          <t>Add Aunt Bea's aside</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Ines</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Agreed.</t>
+          <t>Ditto.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46273</v>
+        <v>46255</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ED-15</t>
+          <t>ED-19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PS-20</t>
+          <t>PS-28</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Trim the auction catalogue</t>
-        </is>
+          <t>Trim the sermon</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>-5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Ines</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Park until the author has read it.</t>
+          <t>Fine as proposed.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46274</v>
+        <v>46255</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ED-07</t>
+          <t>ED-27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PS-10</t>
+          <t>PS-33</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Add a coda to the market scene</t>
-        </is>
+          <t>Trim the walk to the headland</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Ines</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Author says go ahead.</t>
+          <t>Same call as ED-15.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46274</v>
+        <v>46255</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ED-09</t>
+          <t>ED-28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PS-07</t>
+          <t>PS-34</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Drop the second foghorn paragraph</t>
+          <t>Restore the dedication</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Ines</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Agreed.</t>
+          <t>Leave it with the author.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46275</v>
+        <v>46255</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ED-21</t>
+          <t>ED-29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PS-19</t>
+          <t>PS-30</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Add the harbourmaster's warning</t>
+          <t>Cut the inventory of the chest</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Ines</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Park until the author has read it.</t>
+          <t>Not this time.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ED-13</t>
+          <t>ED-01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PS-16</t>
+          <t>PS-01</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cut the second telling of the wreck</t>
+          <t>Restore the epigraph dropped from the draft</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1346,31 +1361,31 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes, and take the next three lines with it: twelve out.</t>
+          <t>Yes, but six lines, not four.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46276</v>
+        <v>46272</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ED-22</t>
+          <t>ED-20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PS-27</t>
+          <t>PS-02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tighten the reading of the will</t>
+          <t>Drop the repeated greeting</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1385,22 +1400,25 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46276</v>
+        <v>46272</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ED-17</t>
+          <t>ED-30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PS-24</t>
+          <t>PS-21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cut the recipe interlude</t>
-        </is>
+          <t>Add the date to the telegram</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1409,31 +1427,28 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No. The author wants the interlude kept.</t>
+          <t>Ditto.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ED-24</t>
+          <t>ED-03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PS-26</t>
+          <t>PS-04</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Add a postscript to the letter</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>3</v>
+          <t>Cut the dream sequence</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1442,31 +1457,28 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Withdrawn: the letter stays as drafted.</t>
+          <t>On reflection, leave this for the author.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46277</v>
+        <v>46273</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ED-23</t>
+          <t>ED-06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PS-29</t>
+          <t>PS-08</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Restore the last line of the postcard</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>2</v>
+          <t>Restore the two lines of the ferry song</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1481,29 +1493,860 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ED-15</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PS-20</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Trim the auction catalogue</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Park until the author has read it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ED-31</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PS-23</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Tighten the argument at the gate</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>In, but two lines out, not four.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ED-07</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PS-10</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Add a coda to the market scene</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Author says go ahead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ED-09</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PS-07</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Drop the second foghorn paragraph</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Agreed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ED-32</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PS-12</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Restore the verse Maud sings</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Same call as ED-12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ED-39</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PS-09</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Restore the dropped stanza</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Author says go ahead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ED-21</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PS-19</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Add the harbourmaster's warning</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Park until the author has read it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ED-13</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PS-16</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Cut the second telling of the wreck</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes, and take the next three lines with it: twelve out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ED-33</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PS-35</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Cut the aside on the tides</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Agreed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ED-34</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PS-36</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Add the doctor's second visit</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hold it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ED-28</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PS-34</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Restore the dedication</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Take it, at the number Ines had.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ED-22</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PS-27</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Tighten the reading of the will</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Agreed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ED-17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PS-24</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Cut the recipe interlude</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>No. The author wants the interlude kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ED-24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PS-26</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Add a postscript to the letter</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Withdrawn: the letter stays as drafted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ED-35</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PS-37</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Drop the second mention of the bell</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ditto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ED-36</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PS-38</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Cut the list of guests</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cut, but four lines only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ED-40</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PS-17</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Cut the description of the pier</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Same call as ED-24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
         <v>46277</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ED-23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PS-29</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Restore the last line of the postcard</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Agreed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>ED-15</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>PS-20</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Trim the auction catalogue</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tomas</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Back to Ines's call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ED-37</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PS-39</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Add the reply to the telegram</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Go ahead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ED-38</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PS-40</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Trim the closing paragraph</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Leave it with the author.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ED-42</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PS-31</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Add the chapel bell</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ditto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ED-25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PS-31</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Cut the second description of the chapel</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>As Ines had it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ED-43</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PS-33</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Cut the second view from the headland</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Same call as ED-33.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ED-44</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PS-05</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Trim the account of the journey</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Not this time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ED-45</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PS-38</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Add the toast</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Go ahead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ED-27</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PS-33</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Trim the walk to the headland</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>Back to Ines's call.</t>
         </is>
@@ -1546,7 +2389,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>A call is one of three. Accepted: the edit goes in, with the number of lines the decision gives, or, if it gives none, the edit's number as it last stood. Deferred: the edit is parked for the author; it does not go in, and it stays open against its passage. Withdrawn: the edit is turned down; it does not go in, and nothing stays open. A decision that returns an edit to an earlier call makes the edit stand as that call did.</t>
+          <t>A call is one of three. Accepted: the edit goes in, with the number of lines the decision gives, or, if it gives none, the edit's number as it last stood. Deferred: the edit is parked for the author; it does not go in, and it stays open against its passage. Withdrawn: the edit is turned down; it does not go in, and nothing stays open. A decision that returns an edit to an earlier call makes the edit stand as that call did. A decision given as the same call as another decision makes the same kind of call, at this edit's own number.</t>
         </is>
       </c>
     </row>
@@ -1578,7 +2421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="3" max="3"/>
@@ -1720,6 +2563,159 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ED-29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PS-30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cut the inventory of the chest</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ED-32</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PS-12</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Restore the verse Maud sings</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ED-34</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PS-36</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Add the doctor's second visit</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ED-35</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PS-37</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Drop the second mention of the bell</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ED-38</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PS-40</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Trim the closing paragraph</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ED-40</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PS-17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cut the description of the pier</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ED-41</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PS-14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Add the ferryman's line</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ED-42</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PS-31</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Add the chapel bell</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ED-44</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PS-05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Trim the account of the journey</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/writing-b52-a9-manuscript-page-ledger-recompute/environment/input/edit_register.xlsx
+++ b/writing-b52-a9-manuscript-page-ledger-recompute/environment/input/edit_register.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="About" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Not in" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Draft pages" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Not in" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2406,7 +2407,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Not in: Tomas's list, at the end of the second read, of the edits that are not going into this pass.</t>
+          <t>Draft pages: Tomas's register of every flag against the draft's pages (30 lines a page, the draft as it stood before either read), for checking off. Not in: Tomas's list, at the end of the second read, of the edits that are not going into this pass.</t>
         </is>
       </c>
     </row>
@@ -2416,6 +2417,915 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>passage_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>draft_line</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>drafted_lines</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>draft_page</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PS-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PS-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PS-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PS-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PS-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>62</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PS-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>83</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PS-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PS-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>115</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PS-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>126</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PS-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>142</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PS-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>150</v>
+      </c>
+      <c r="C12" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PS-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>167</v>
+      </c>
+      <c r="C13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PS-13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>194</v>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PS-14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>214</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PS-15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>220</v>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PS-16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>235</v>
+      </c>
+      <c r="C17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PS-17</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>268</v>
+      </c>
+      <c r="C18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PS-18</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>283</v>
+      </c>
+      <c r="C19" t="n">
+        <v>19</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PS-19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>302</v>
+      </c>
+      <c r="C20" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PS-20</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>320</v>
+      </c>
+      <c r="C21" t="n">
+        <v>27</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PS-21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>347</v>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>12</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PS-22</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>356</v>
+      </c>
+      <c r="C23" t="n">
+        <v>14</v>
+      </c>
+      <c r="D23" t="n">
+        <v>12</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PS-23</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>370</v>
+      </c>
+      <c r="C24" t="n">
+        <v>23</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PS-24</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>393</v>
+      </c>
+      <c r="C25" t="n">
+        <v>11</v>
+      </c>
+      <c r="D25" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PS-25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>404</v>
+      </c>
+      <c r="C26" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PS-26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>420</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PS-27</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>427</v>
+      </c>
+      <c r="C28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PS-28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>466</v>
+      </c>
+      <c r="C29" t="n">
+        <v>13</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PS-29</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>479</v>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PS-30</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>489</v>
+      </c>
+      <c r="C31" t="n">
+        <v>19</v>
+      </c>
+      <c r="D31" t="n">
+        <v>17</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PS-31</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>520</v>
+      </c>
+      <c r="C32" t="n">
+        <v>14</v>
+      </c>
+      <c r="D32" t="n">
+        <v>18</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PS-32</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>534</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>18</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PS-33</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>542</v>
+      </c>
+      <c r="C34" t="n">
+        <v>17</v>
+      </c>
+      <c r="D34" t="n">
+        <v>19</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PS-34</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>569</v>
+      </c>
+      <c r="C35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D35" t="n">
+        <v>19</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PS-35</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>74</v>
+      </c>
+      <c r="C36" t="n">
+        <v>9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PS-36</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>180</v>
+      </c>
+      <c r="C37" t="n">
+        <v>14</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PS-37</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>314</v>
+      </c>
+      <c r="C38" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" t="n">
+        <v>11</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PS-16</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>259</v>
+      </c>
+      <c r="C39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D39" t="n">
+        <v>9</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PS-38</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>448</v>
+      </c>
+      <c r="C40" t="n">
+        <v>18</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PS-39</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>508</v>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="n">
+        <v>17</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>over a break</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PS-40</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>559</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="n">
+        <v>19</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>on one page</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
